--- a/patient_list.xlsx
+++ b/patient_list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhennongchen/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhennongchen/Documents/GitHub/Diffusion_for_CT_motion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05898C97-2A56-EB41-99DE-490894FF389C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AF6544-ED3A-C542-9FF1-EEE55F8A28AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="500" windowWidth="28800" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,13 +40,13 @@
     <t>case_B</t>
   </si>
   <si>
-    <t>/mnt/camca_NAS/diffusion_ct_motion/github_example_data/case_A/reference.nii.gz</t>
-  </si>
-  <si>
-    <t>/mnt/camca_NAS/diffusion_ct_motion/github_example_data/case_A/motion.nii.gz</t>
-  </si>
-  <si>
-    <t>/mnt/camca_NAS/diffusion_ct_motion/github_example_data/case_B/motion.nii.gz</t>
+    <t>github_example_data/case_A/reference.nii.gz</t>
+  </si>
+  <si>
+    <t>github_example_data/case_A/motion.nii.gz</t>
+  </si>
+  <si>
+    <t>github_example_data/case_B/motion.nii.gz</t>
   </si>
 </sst>
 </file>
